--- a/outputs_xlsx_solution/test_new1.4-wide-NC-1.xlsx
+++ b/outputs_xlsx_solution/test_new1.4-wide-NC-1.xlsx
@@ -71,6 +71,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>IS</t>
   </si>
   <si>
@@ -117,6 +120,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -570,7 +576,7 @@
         <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -590,13 +596,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -616,13 +622,13 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -642,13 +648,19 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
         <v>12</v>
       </c>
       <c r="I5" t="s">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -668,13 +680,13 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6" t="s">
         <v>11</v>
       </c>
       <c r="K6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -697,7 +709,7 @@
         <v>11</v>
       </c>
       <c r="N7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -717,13 +729,13 @@
         <v>9</v>
       </c>
       <c r="M8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N8" t="s">
         <v>11</v>
       </c>
       <c r="O8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -743,13 +755,13 @@
         <v>9</v>
       </c>
       <c r="M9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O9" t="s">
         <v>11</v>
       </c>
       <c r="P9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -769,16 +781,16 @@
         <v>9</v>
       </c>
       <c r="N10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O10" t="s">
         <v>11</v>
       </c>
       <c r="P10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -798,16 +810,19 @@
         <v>9</v>
       </c>
       <c r="N11" t="s">
+        <v>13</v>
+      </c>
+      <c r="O11" t="s">
         <v>12</v>
       </c>
       <c r="P11" t="s">
         <v>11</v>
       </c>
       <c r="Q11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -827,16 +842,16 @@
         <v>9</v>
       </c>
       <c r="N12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q12" t="s">
         <v>11</v>
       </c>
       <c r="R12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -856,16 +871,16 @@
         <v>9</v>
       </c>
       <c r="O13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q13" t="s">
         <v>11</v>
       </c>
       <c r="R13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -885,16 +900,19 @@
         <v>9</v>
       </c>
       <c r="O14" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q14" t="s">
         <v>12</v>
       </c>
       <c r="R14" t="s">
         <v>11</v>
       </c>
       <c r="S14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -914,19 +932,19 @@
         <v>9</v>
       </c>
       <c r="O15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S15" t="s">
         <v>11</v>
       </c>
       <c r="T15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -946,16 +964,16 @@
         <v>9</v>
       </c>
       <c r="P16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S16" t="s">
         <v>11</v>
       </c>
       <c r="T16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -975,19 +993,22 @@
         <v>9</v>
       </c>
       <c r="P17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q17" t="s">
+        <v>13</v>
+      </c>
+      <c r="S17" t="s">
         <v>12</v>
       </c>
       <c r="T17" t="s">
         <v>11</v>
       </c>
       <c r="U17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -1007,24 +1028,24 @@
         <v>9</v>
       </c>
       <c r="Q18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U18" t="s">
         <v>11</v>
       </c>
       <c r="V18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1032,7 +1053,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1040,15 +1061,15 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -1056,39 +1077,55 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
         <v>26</v>
       </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
         <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
